--- a/Result/profitability/5009.xlsx
+++ b/Result/profitability/5009.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>0.695</v>
+        <v>0.54875</v>
       </c>
       <c r="N2" t="n">
-        <v>22.62625</v>
+        <v>22.25</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5287500000000001</v>
+        <v>0.525</v>
       </c>
       <c r="N3" t="n">
-        <v>21.57875</v>
+        <v>21.35125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5625</v>
+        <v>0.54625</v>
       </c>
       <c r="N4" t="n">
-        <v>20.45375</v>
+        <v>20.4225</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.79</v>
       </c>
       <c r="M5" t="n">
-        <v>0.385</v>
+        <v>0.40125</v>
       </c>
       <c r="N5" t="n">
-        <v>17.13625</v>
+        <v>17.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2925</v>
+        <v>0.3175</v>
       </c>
       <c r="N6" t="n">
-        <v>14.62125</v>
+        <v>15.21125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>0.21625</v>
+        <v>0.1675</v>
       </c>
       <c r="N7" t="n">
-        <v>13.06375</v>
+        <v>13.14125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0.08625000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>10.50125</v>
+        <v>10.43</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.18875</v>
       </c>
       <c r="N12" t="n">
-        <v>6.335000000000001</v>
+        <v>6.334999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.05125000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>8.7575</v>
+        <v>8.757499999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3214</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2449</v>
+      </c>
+      <c r="E75" t="n">
+        <v>765</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>380</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>382</v>
+      </c>
+      <c r="K75" t="n">
+        <v>281</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.67375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.435</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5700000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02337981952420021</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3513513513513513</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.309999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1614634146341463</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
